--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/08_Anotacijos_logai/08_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/08_Anotacijos_logai/08_Anotavimo_logas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\08_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33A67B3-D1B9-4AC5-A3EB-3650C467EBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6134C10E-E57A-46A3-BB70-69750A87E702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="1380" windowWidth="18600" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-260" yWindow="960" windowWidth="18600" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="logas" sheetId="2" r:id="rId1"/>
@@ -289,7 +289,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -655,7 +655,9 @@
       <c r="D2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="4"/>
+      <c r="E2" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="F2" s="4"/>
       <c r="G2" s="3" t="s">
         <v>30</v>
@@ -689,7 +691,9 @@
       <c r="D3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="3" t="s">
         <v>30</v>
@@ -724,7 +728,9 @@
       <c r="D4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="F4" s="4"/>
       <c r="G4" s="3" t="s">
         <v>30</v>
@@ -757,7 +763,9 @@
       <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="3" t="s">
         <v>30</v>
@@ -792,7 +800,9 @@
       <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="F6" s="4"/>
       <c r="G6" s="3" t="s">
         <v>30</v>
@@ -827,7 +837,9 @@
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="G7" s="3" t="s">
         <v>30</v>
@@ -862,7 +874,9 @@
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="3" t="s">
         <v>30</v>

--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/08_Anotacijos_logai/08_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/08_Anotacijos_logai/08_Anotavimo_logas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\08_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6134C10E-E57A-46A3-BB70-69750A87E702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75B8887-C723-44A5-AA25-83F782E85AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-260" yWindow="960" windowWidth="18600" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="18600" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="logas" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="47">
   <si>
     <t>basename</t>
   </si>
@@ -171,6 +171,12 @@
   </si>
   <si>
     <t>1025_2</t>
+  </si>
+  <si>
+    <t>Ž:  Kelis kartus po skilvelinės ekstrasistolės šiame įraše stebime vadinamus "fusion beat" (susiliejęs kompleksas). Jį lemia tai, jog skilvelių depoliarizaciją lemia tiek neseniai buvusi skilvelinė ekstrasistolė, tiek iš sinusinio mazgo atėjęs impulsas ir šios dvi skilvelio aktyvacijos susilieja, todėl keičia morfologiją, palyginus su įprastu sinusiniu kompleksu, tačiau nėra platus kaip skilvelinė ekstrasistolė. Šiuo atveju tai nėra nei skilvelinė, nei prieširdinė ekstrasistolės, nei normalus QRS kompleksas. Tam, kad neklaidinti algoritmo pažymėjau juos U raide.</t>
+  </si>
+  <si>
+    <t>1643055.090</t>
   </si>
 </sst>
 </file>
@@ -224,7 +230,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -262,11 +268,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -291,6 +308,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -572,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
@@ -655,14 +679,16 @@
       <c r="D2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="6" t="s">
@@ -677,6 +703,9 @@
       <c r="N2" t="s">
         <v>28</v>
       </c>
+      <c r="O2" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
@@ -691,14 +720,16 @@
       <c r="D3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="6" t="s">
@@ -728,14 +759,16 @@
       <c r="D4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="6"/>
@@ -763,14 +796,16 @@
       <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="6" t="s">
@@ -800,14 +835,16 @@
       <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="6" t="s">
@@ -837,14 +874,16 @@
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="6" t="s">
@@ -874,14 +913,16 @@
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="G8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="4"/>
+      <c r="H8" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="6" t="s">
@@ -896,6 +937,26 @@
       <c r="N8" t="str">
         <f>""</f>
         <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/08_Anotacijos_logai/08_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/08_Anotacijos_logai/08_Anotavimo_logas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\08_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75B8887-C723-44A5-AA25-83F782E85AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7CB06F-2DB1-4A38-913A-3B311F4C126B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="18600" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="logas" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
   <si>
     <t>basename</t>
   </si>
@@ -122,9 +122,6 @@
     <t>Žygimantas</t>
   </si>
   <si>
-    <t>Vietomis nedidelis virpėjimas, galimas demo Nikai</t>
-  </si>
-  <si>
     <t>Po anotacijos</t>
   </si>
   <si>
@@ -177,6 +174,24 @@
   </si>
   <si>
     <t>1643055.090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pažymėtas Nikos, kaip 3333, nors dalis sužymėtų triukšmų yra tik bangelės. Aš jį pažymėjau kaip kandidatą į 1111. Reiktų aptarti </t>
+  </si>
+  <si>
+    <t>ir mano, ir Nikos pažymėtas, kaip 3333, tačiau ar reikėjo pažymėti visą kaip triukšmą - klausimas, gal nuimti tai - aš nuėmiau ir pažymėjau, kad triukšmai nepažymėti</t>
+  </si>
+  <si>
+    <t>Nika pažymėjo, kaip 2222, aš jį priskiriau prie 1111 ir tinkamo mokymui.</t>
+  </si>
+  <si>
+    <t>Labai švarus</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kokybė 3333, Nika sužymėjo triukšmus, tačiau aš juos panaikinau, nėra prasmės</t>
+  </si>
+  <si>
+    <t>Nika priskyrė 3333, sužymėjo triukšmą, mano požiūris - 2222</t>
   </si>
 </sst>
 </file>
@@ -313,7 +328,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -656,7 +671,7 @@
         <v>26</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
@@ -671,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>27</v>
@@ -684,12 +699,11 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="I2" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="J2" s="4"/>
       <c r="K2" s="6" t="s">
         <v>3</v>
@@ -701,10 +715,10 @@
         <v>2</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="O2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -712,10 +726,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>27</v>
@@ -725,11 +739,9 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="4" t="b">
-        <v>1</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="6" t="s">
@@ -741,9 +753,8 @@
       <c r="M3" t="s">
         <v>6</v>
       </c>
-      <c r="N3" t="str">
-        <f>""</f>
-        <v/>
+      <c r="N3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -751,10 +762,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>27</v>
@@ -764,23 +775,25 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="6"/>
+        <v>29</v>
+      </c>
+      <c r="I4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="L4" t="s">
         <v>8</v>
       </c>
       <c r="M4" t="s">
         <v>9</v>
       </c>
-      <c r="N4" t="str">
-        <f>""</f>
-        <v/>
+      <c r="N4">
+        <v>1111</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -788,10 +801,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>27</v>
@@ -801,13 +814,14 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="I5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="K5" s="6" t="s">
         <v>12</v>
       </c>
@@ -817,9 +831,8 @@
       <c r="M5" t="s">
         <v>11</v>
       </c>
-      <c r="N5" t="str">
-        <f>""</f>
-        <v/>
+      <c r="N5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -827,10 +840,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>27</v>
@@ -840,13 +853,14 @@
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="I6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="K6" s="6" t="s">
         <v>15</v>
       </c>
@@ -856,9 +870,8 @@
       <c r="M6" t="s">
         <v>14</v>
       </c>
-      <c r="N6" t="str">
-        <f>""</f>
-        <v/>
+      <c r="N6" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -866,10 +879,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
@@ -879,11 +892,9 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="4" t="b">
-        <v>1</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="6" t="s">
@@ -895,9 +906,8 @@
       <c r="M7" t="s">
         <v>14</v>
       </c>
-      <c r="N7" t="str">
-        <f>""</f>
-        <v/>
+      <c r="N7" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -905,10 +915,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
@@ -918,12 +928,11 @@
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="I8" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="6" t="s">
         <v>15</v>
@@ -934,9 +943,8 @@
       <c r="M8" t="s">
         <v>14</v>
       </c>
-      <c r="N8" t="str">
-        <f>""</f>
-        <v/>
+      <c r="N8">
+        <v>2222</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
@@ -944,7 +952,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -953,10 +961,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
